--- a/Unified_PDF_Platform/uploads/extracted_data_structural.xlsx
+++ b/Unified_PDF_Platform/uploads/extracted_data_structural.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,6110 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CHEINE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ALEXANDER</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>COLLYMORE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MOESHA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MALAVET</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JORDAN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PACHECOMORILLO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OSCAR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>32</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GERHART</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ORR</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NICHOLAS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-53.53</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FRANK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-33.76</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WINTERS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MITCHELL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PINGEL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TREVOR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PINGEL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TREVOR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-17.31</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PINGEL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TREVOR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CATHERINE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Balingit</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AlecJ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Balingit</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AlecJ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Balingit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AlecJ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Balingit</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AlecJ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Boghosian</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boghosian</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Boghosian</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Boghosian</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bonsack</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bonsack</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bonsack</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bonsack</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Carney</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DakotaM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Carney</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DakotaM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Carney</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DakotaM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Carney</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DakotaM</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cheine</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>AlexanderB</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cheine</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AlexanderB</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cheine</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AlexanderB</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cheine</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AlexanderB</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Collymore</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MoeshaT</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Collymore</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MoeshaT</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Collymore</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MoeshaT</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Collymore</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MoeshaT</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Crouch</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TherralR</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Crouch</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TherralR</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Crouch</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TherralR</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Crouch</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TherralR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Fayson</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bryonne</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Fayson</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bryonne</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Fayson</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bryonne</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Fayson</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bryonne</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Gerhart</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PaulR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Gerhart</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PaulR</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Gerhart</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PaulR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Graves</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CarsonJ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Graves</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CarsonJ</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Graves</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CarsonJ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Graves</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CarsonJ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PaytonL</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PaytonL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PaytonL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PaytonL</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>23</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>JeanLouis</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Roody</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>JeanLouis</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Roody</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JeanLouis</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Roody</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>JeanLouis</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Roody</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LegaspiCisnero</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LegaspiCisnero</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LegaspiCisnero</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LegaspiCisnero</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Malavet</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Malavet</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Malavet</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Malavet</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Massaad</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Massaad</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Massaad</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Massaad</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Mckee</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Maxwell</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Mckee</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Maxwell</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Mckee</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Maxwell</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Mckee</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Maxwell</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Micenec</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MatthewR</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Micenec</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MatthewR</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Micenec</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MatthewR</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Micenec</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MatthewR</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Noskey</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Noskey</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Noskey</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Noskey</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Orr</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Orr</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Orr</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ortiz-Hernandez</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Alfredo</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ortiz-Hernandez</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Alfredo</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ortiz-Hernandez</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Alfredo</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ortiz-Hernandez</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Alfredo</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PachecoMorillo</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PachecoMorillo</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PachecoMorillo</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PachecoMorillo</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Proechel</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Proechel</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Proechel</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Proechel</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>KristianL</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>KristianL</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>KristianL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>KristianL</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>DanielA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>DanielA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>DanielA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DanielA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Stealey</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Stealey</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Stealey</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Stealey</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Tovar</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>44</v>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Tovar</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Tovar</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Winters</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Winters</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Winters</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Yoder</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>GaryM</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Yoder</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>GaryM</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Yoder</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>GaryM</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Yoder</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>GaryM</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Zwetsch</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Employee BasicTermLife</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Zwetsch</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Zwetsch</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guardian Rocca Feb-25 Inv.pdf</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>01/17/25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>02/01/25to02/28/25</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Zwetsch</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>709.78</v>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Unified_PDF_Platform/uploads/extracted_data_structural.xlsx
+++ b/Unified_PDF_Platform/uploads/extracted_data_structural.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="193">
   <si>
     <t>SOURCE_FILE</t>
   </si>
@@ -64,343 +64,535 @@
     <t>PRICING_ADJUSTMENT</t>
   </si>
   <si>
-    <t>BCBS- 23 Rests- div001- Feb 26.pdf</t>
+    <t>BCBS- 23 Rests- div003- Feb 26.pdf</t>
   </si>
   <si>
     <t>02/01/2026</t>
   </si>
   <si>
-    <t>78238568</t>
+    <t>78238570</t>
   </si>
   <si>
     <t>02/01/2026-03/01/2026</t>
   </si>
   <si>
-    <t>BROWN</t>
-  </si>
-  <si>
-    <t>CLOSE</t>
-  </si>
-  <si>
-    <t>COLLIN</t>
-  </si>
-  <si>
-    <t>DAKE</t>
-  </si>
-  <si>
-    <t>DAVENPORT</t>
-  </si>
-  <si>
-    <t>DUQUETTE</t>
-  </si>
-  <si>
-    <t>EMRICH</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>FERRELL</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>HOLDER</t>
-  </si>
-  <si>
-    <t>HORSEMAN</t>
-  </si>
-  <si>
-    <t>LAQUERRE</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MCNORRILL</t>
-  </si>
-  <si>
-    <t>MOYE</t>
-  </si>
-  <si>
-    <t>NICCUM</t>
-  </si>
-  <si>
-    <t>ROMANO</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>SELF</t>
-  </si>
-  <si>
-    <t>SHORT</t>
-  </si>
-  <si>
-    <t>WEAVER</t>
-  </si>
-  <si>
-    <t>ZINDA</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ERIC</t>
-  </si>
-  <si>
-    <t>JUSTIN</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>TRACEY</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>TRANESHA</t>
-  </si>
-  <si>
-    <t>KAYLEE</t>
-  </si>
-  <si>
-    <t>NIKKI</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>STACEY</t>
-  </si>
-  <si>
-    <t>LORI</t>
+    <t>AMES</t>
+  </si>
+  <si>
+    <t>AMORUSO</t>
+  </si>
+  <si>
+    <t>ASBURY</t>
+  </si>
+  <si>
+    <t>BARNETT</t>
+  </si>
+  <si>
+    <t>BLAIR</t>
+  </si>
+  <si>
+    <t>BRANNOCK</t>
+  </si>
+  <si>
+    <t>CAIVANO</t>
+  </si>
+  <si>
+    <t>DE-BORJA</t>
+  </si>
+  <si>
+    <t>DELELLIS</t>
+  </si>
+  <si>
+    <t>EBY</t>
+  </si>
+  <si>
+    <t>FETT</t>
+  </si>
+  <si>
+    <t>FOURNIER</t>
+  </si>
+  <si>
+    <t>FOX</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOLDYN</t>
+  </si>
+  <si>
+    <t>GOVER</t>
+  </si>
+  <si>
+    <t>HENDERSON</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>HOLTON</t>
+  </si>
+  <si>
+    <t>HURLBURT</t>
+  </si>
+  <si>
+    <t>KENWOOD</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>KOVALCHICK</t>
+  </si>
+  <si>
+    <t>LEMOS</t>
+  </si>
+  <si>
+    <t>LINDAUER</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MARSHALL</t>
+  </si>
+  <si>
+    <t>MCCABE</t>
+  </si>
+  <si>
+    <t>MOISE</t>
+  </si>
+  <si>
+    <t>NOONAN</t>
+  </si>
+  <si>
+    <t>PENA</t>
+  </si>
+  <si>
+    <t>PFENNINGER</t>
+  </si>
+  <si>
+    <t>POW</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROUSE</t>
+  </si>
+  <si>
+    <t>SCHULZ</t>
+  </si>
+  <si>
+    <t>SMITH</t>
+  </si>
+  <si>
+    <t>TUCKER</t>
+  </si>
+  <si>
+    <t>VAN-MANEN</t>
+  </si>
+  <si>
+    <t>WOOD</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>SEBASTIEN</t>
+  </si>
+  <si>
+    <t>MARK</t>
+  </si>
+  <si>
+    <t>JULIANA</t>
+  </si>
+  <si>
+    <t>MORGAN</t>
+  </si>
+  <si>
+    <t>JASON</t>
+  </si>
+  <si>
+    <t>MATTHEW</t>
+  </si>
+  <si>
+    <t>ALEX</t>
+  </si>
+  <si>
+    <t>ANNE</t>
+  </si>
+  <si>
+    <t>RICHARD</t>
+  </si>
+  <si>
+    <t>MASON</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>CHELSEA</t>
   </si>
   <si>
     <t>NICK</t>
   </si>
   <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>AMANDA</t>
-  </si>
-  <si>
-    <t>KATIE</t>
-  </si>
-  <si>
-    <t>REMINGTON</t>
-  </si>
-  <si>
-    <t>KELLY</t>
-  </si>
-  <si>
-    <t>CELESTE</t>
-  </si>
-  <si>
-    <t>REBEL</t>
-  </si>
-  <si>
-    <t>KRISTIAN</t>
-  </si>
-  <si>
-    <t>ANDREW</t>
-  </si>
-  <si>
-    <t>LYNE</t>
+    <t>JAMIEN</t>
+  </si>
+  <si>
+    <t>CHEYENNE</t>
+  </si>
+  <si>
+    <t>KARISSA</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>JENNA</t>
+  </si>
+  <si>
+    <t>MARIE</t>
+  </si>
+  <si>
+    <t>EMMA</t>
+  </si>
+  <si>
+    <t>NICOLE</t>
+  </si>
+  <si>
+    <t>MICHAEL</t>
+  </si>
+  <si>
+    <t>HAROLD</t>
+  </si>
+  <si>
+    <t>BYRAN</t>
+  </si>
+  <si>
+    <t>BRIAN</t>
+  </si>
+  <si>
+    <t>JOSEPH</t>
+  </si>
+  <si>
+    <t>KRISTIN</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ROBERT</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>CHRISTOPHE</t>
+  </si>
+  <si>
+    <t>ALFRED</t>
+  </si>
+  <si>
+    <t>JOHNNIE</t>
+  </si>
+  <si>
+    <t>ROY</t>
+  </si>
+  <si>
+    <t>CAROLINE</t>
+  </si>
+  <si>
+    <t>SPENCER</t>
+  </si>
+  <si>
+    <t>HOWARD</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>D</t>
+    <t>J</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>B</t>
+    <t>S</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>K</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>9868</t>
-  </si>
-  <si>
-    <t>6597</t>
-  </si>
-  <si>
-    <t>1399</t>
-  </si>
-  <si>
-    <t>2149</t>
-  </si>
-  <si>
-    <t>2085</t>
-  </si>
-  <si>
-    <t>3290</t>
-  </si>
-  <si>
-    <t>2877</t>
-  </si>
-  <si>
-    <t>5673</t>
-  </si>
-  <si>
-    <t>9122</t>
-  </si>
-  <si>
-    <t>7111</t>
-  </si>
-  <si>
-    <t>2768</t>
-  </si>
-  <si>
-    <t>1540</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>7905</t>
+    <t>I</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>5531</t>
+  </si>
+  <si>
+    <t>4625</t>
+  </si>
+  <si>
+    <t>2058</t>
+  </si>
+  <si>
+    <t>4602</t>
+  </si>
+  <si>
+    <t>7407</t>
+  </si>
+  <si>
+    <t>4234</t>
+  </si>
+  <si>
+    <t>2751</t>
+  </si>
+  <si>
+    <t>6945</t>
+  </si>
+  <si>
+    <t>8426</t>
+  </si>
+  <si>
+    <t>4610</t>
+  </si>
+  <si>
+    <t>5213</t>
+  </si>
+  <si>
+    <t>2955</t>
+  </si>
+  <si>
+    <t>1570</t>
+  </si>
+  <si>
+    <t>4487</t>
+  </si>
+  <si>
+    <t>6712</t>
+  </si>
+  <si>
+    <t>7814</t>
+  </si>
+  <si>
+    <t>4210</t>
+  </si>
+  <si>
+    <t>1425</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>6291</t>
+  </si>
+  <si>
+    <t>9705</t>
+  </si>
+  <si>
+    <t>8997</t>
+  </si>
+  <si>
+    <t>9822</t>
+  </si>
+  <si>
+    <t>4756</t>
+  </si>
+  <si>
+    <t>9059</t>
+  </si>
+  <si>
+    <t>3848</t>
+  </si>
+  <si>
+    <t>3757</t>
+  </si>
+  <si>
+    <t>9619</t>
+  </si>
+  <si>
+    <t>7255</t>
+  </si>
+  <si>
+    <t>7115</t>
+  </si>
+  <si>
+    <t>5270</t>
+  </si>
+  <si>
+    <t>2220</t>
+  </si>
+  <si>
+    <t>4266</t>
+  </si>
+  <si>
+    <t>5594</t>
   </si>
   <si>
     <t>0579</t>
   </si>
   <si>
-    <t>3004</t>
-  </si>
-  <si>
-    <t>1292</t>
-  </si>
-  <si>
-    <t>8274</t>
-  </si>
-  <si>
-    <t>0649</t>
-  </si>
-  <si>
-    <t>7582</t>
-  </si>
-  <si>
-    <t>7749</t>
-  </si>
-  <si>
-    <t>5536</t>
-  </si>
-  <si>
-    <t>2387</t>
-  </si>
-  <si>
-    <t>8086</t>
-  </si>
-  <si>
-    <t>H82925092</t>
-  </si>
-  <si>
-    <t>H48088910</t>
-  </si>
-  <si>
-    <t>H31228769</t>
-  </si>
-  <si>
-    <t>H99053768</t>
-  </si>
-  <si>
-    <t>H46288578</t>
-  </si>
-  <si>
-    <t>H46287830</t>
-  </si>
-  <si>
-    <t>H31326995</t>
-  </si>
-  <si>
-    <t>H46288514</t>
-  </si>
-  <si>
-    <t>H46288433</t>
-  </si>
-  <si>
-    <t>H46287993</t>
-  </si>
-  <si>
-    <t>H48088947</t>
-  </si>
-  <si>
-    <t>H46288253</t>
-  </si>
-  <si>
-    <t>H68211054</t>
-  </si>
-  <si>
-    <t>H25650965</t>
-  </si>
-  <si>
-    <t>H46288181</t>
-  </si>
-  <si>
-    <t>H48088974</t>
-  </si>
-  <si>
-    <t>H48088992</t>
-  </si>
-  <si>
-    <t>H48089009</t>
-  </si>
-  <si>
-    <t>H39442357</t>
-  </si>
-  <si>
-    <t>H46470971</t>
-  </si>
-  <si>
-    <t>H46288370</t>
-  </si>
-  <si>
-    <t>H46471006</t>
-  </si>
-  <si>
-    <t>H46288082</t>
-  </si>
-  <si>
-    <t>H51821758</t>
+    <t>8865</t>
+  </si>
+  <si>
+    <t>3259</t>
+  </si>
+  <si>
+    <t>5333</t>
+  </si>
+  <si>
+    <t>7507</t>
+  </si>
+  <si>
+    <t>0227</t>
+  </si>
+  <si>
+    <t>2196</t>
+  </si>
+  <si>
+    <t>H48088794</t>
+  </si>
+  <si>
+    <t>H46288596</t>
+  </si>
+  <si>
+    <t>H93424582</t>
+  </si>
+  <si>
+    <t>H41569003</t>
+  </si>
+  <si>
+    <t>H46288523</t>
+  </si>
+  <si>
+    <t>H26617024</t>
+  </si>
+  <si>
+    <t>H26637436</t>
+  </si>
+  <si>
+    <t>H39901709</t>
+  </si>
+  <si>
+    <t>H48088929</t>
+  </si>
+  <si>
+    <t>H46288208</t>
+  </si>
+  <si>
+    <t>H25284359</t>
+  </si>
+  <si>
+    <t>H46287821</t>
+  </si>
+  <si>
+    <t>H46747884</t>
+  </si>
+  <si>
+    <t>H46288550</t>
+  </si>
+  <si>
+    <t>H46287876</t>
+  </si>
+  <si>
+    <t>H46288073</t>
+  </si>
+  <si>
+    <t>H23758427</t>
+  </si>
+  <si>
+    <t>H46288451</t>
+  </si>
+  <si>
+    <t>H46288587</t>
+  </si>
+  <si>
+    <t>H82847521</t>
+  </si>
+  <si>
+    <t>H41035546</t>
+  </si>
+  <si>
+    <t>H46288316</t>
+  </si>
+  <si>
+    <t>H46288028</t>
+  </si>
+  <si>
+    <t>H48088956</t>
+  </si>
+  <si>
+    <t>H46288280</t>
+  </si>
+  <si>
+    <t>H48088965</t>
+  </si>
+  <si>
+    <t>H46288127</t>
+  </si>
+  <si>
+    <t>H26687990</t>
+  </si>
+  <si>
+    <t>H46288613</t>
+  </si>
+  <si>
+    <t>H38028890</t>
+  </si>
+  <si>
+    <t>H82950742</t>
+  </si>
+  <si>
+    <t>H98759379</t>
+  </si>
+  <si>
+    <t>H46288505</t>
+  </si>
+  <si>
+    <t>H20152467</t>
+  </si>
+  <si>
+    <t>H46862363</t>
+  </si>
+  <si>
+    <t>H46288136</t>
+  </si>
+  <si>
+    <t>H48281032</t>
+  </si>
+  <si>
+    <t>H46288299</t>
+  </si>
+  <si>
+    <t>H46288334</t>
+  </si>
+  <si>
+    <t>H48089036</t>
+  </si>
+  <si>
+    <t>H28823203</t>
   </si>
   <si>
     <t>BLUECARE NFQ</t>
   </si>
   <si>
     <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>EC</t>
   </si>
 </sst>
 </file>
@@ -758,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -828,22 +1020,19 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="K2" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N2">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -863,22 +1052,19 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="K3" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N3">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -898,19 +1084,22 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
+        <v>99</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="K4" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N4">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -930,22 +1119,19 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="J5" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="K5" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N5">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -965,22 +1151,19 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="J6" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="K6" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N6">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1000,22 +1183,22 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="J7" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="K7" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N7">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1035,22 +1218,19 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="J8" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="K8" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N8">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1070,19 +1250,19 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="J9" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="K9" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N9">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1102,19 +1282,22 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>67</v>
+      </c>
+      <c r="G10" t="s">
+        <v>101</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="J10" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="K10" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N10">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1134,19 +1317,22 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>102</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="J11" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="K11" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N11">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1166,22 +1352,22 @@
         <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="J12" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="K12" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N12">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1201,22 +1387,22 @@
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="J13" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="K13" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="N13">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1236,22 +1422,25 @@
         <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
+        <v>99</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="J14" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="K14" t="s">
-        <v>125</v>
-      </c>
-      <c r="M14" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N14">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
+      </c>
+      <c r="O14">
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1271,22 +1460,22 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="J15" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
-      </c>
-      <c r="M15" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N15">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1306,25 +1495,22 @@
         <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="H16" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="J16" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="K16" t="s">
-        <v>125</v>
-      </c>
-      <c r="M16" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N16">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1344,25 +1530,22 @@
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="J17" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="K17" t="s">
-        <v>125</v>
-      </c>
-      <c r="M17" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="N17">
-        <v>1482.6</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1382,25 +1565,19 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="J18" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="K18" t="s">
-        <v>125</v>
-      </c>
-      <c r="M18" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N18">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1420,22 +1597,22 @@
         <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>102</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="K19" t="s">
-        <v>125</v>
-      </c>
-      <c r="M19" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N19">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1455,25 +1632,22 @@
         <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="K20" t="s">
-        <v>125</v>
-      </c>
-      <c r="M20" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="N20">
-        <v>1482.6</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1493,25 +1667,19 @@
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="J21" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="K21" t="s">
-        <v>125</v>
-      </c>
-      <c r="M21" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N21">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1531,22 +1699,19 @@
         <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="J22" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="K22" t="s">
-        <v>125</v>
-      </c>
-      <c r="M22" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N22">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1566,25 +1731,22 @@
         <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H23" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="J23" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>125</v>
-      </c>
-      <c r="M23" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N23">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1604,25 +1766,22 @@
         <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H24" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J24" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>125</v>
-      </c>
-      <c r="M24" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N24">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1642,30 +1801,595 @@
         <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="G25" t="s">
+        <v>107</v>
       </c>
       <c r="H25" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="J25" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="K25" t="s">
-        <v>125</v>
-      </c>
-      <c r="M25" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N25">
-        <v>741.3099999999999</v>
+        <v>590.1900000000001</v>
       </c>
     </row>
     <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" t="s">
+        <v>174</v>
+      </c>
       <c r="K26" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="N26">
-        <v>11108.36</v>
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" t="s">
+        <v>175</v>
+      </c>
+      <c r="K27" t="s">
+        <v>191</v>
+      </c>
+      <c r="N27">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" t="s">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s">
+        <v>176</v>
+      </c>
+      <c r="K28" t="s">
+        <v>191</v>
+      </c>
+      <c r="N28">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="J29" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" t="s">
+        <v>191</v>
+      </c>
+      <c r="N29">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" t="s">
+        <v>137</v>
+      </c>
+      <c r="J30" t="s">
+        <v>178</v>
+      </c>
+      <c r="K30" t="s">
+        <v>191</v>
+      </c>
+      <c r="N30">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" t="s">
+        <v>179</v>
+      </c>
+      <c r="K31" t="s">
+        <v>191</v>
+      </c>
+      <c r="N31">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="H32" t="s">
+        <v>139</v>
+      </c>
+      <c r="J32" t="s">
+        <v>180</v>
+      </c>
+      <c r="K32" t="s">
+        <v>191</v>
+      </c>
+      <c r="N32">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" t="s">
+        <v>140</v>
+      </c>
+      <c r="J33" t="s">
+        <v>181</v>
+      </c>
+      <c r="K33" t="s">
+        <v>191</v>
+      </c>
+      <c r="N33">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
+        <v>141</v>
+      </c>
+      <c r="J34" t="s">
+        <v>182</v>
+      </c>
+      <c r="K34" t="s">
+        <v>191</v>
+      </c>
+      <c r="N34">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" t="s">
+        <v>183</v>
+      </c>
+      <c r="K35" t="s">
+        <v>191</v>
+      </c>
+      <c r="N35">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" t="s">
+        <v>92</v>
+      </c>
+      <c r="G36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H36" t="s">
+        <v>143</v>
+      </c>
+      <c r="J36" t="s">
+        <v>184</v>
+      </c>
+      <c r="K36" t="s">
+        <v>191</v>
+      </c>
+      <c r="N36">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K37" t="s">
+        <v>191</v>
+      </c>
+      <c r="N37">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" t="s">
+        <v>145</v>
+      </c>
+      <c r="J38" t="s">
+        <v>186</v>
+      </c>
+      <c r="K38" t="s">
+        <v>191</v>
+      </c>
+      <c r="N38">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39" t="s">
+        <v>101</v>
+      </c>
+      <c r="H39" t="s">
+        <v>146</v>
+      </c>
+      <c r="J39" t="s">
+        <v>187</v>
+      </c>
+      <c r="K39" t="s">
+        <v>191</v>
+      </c>
+      <c r="N39">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" t="s">
+        <v>96</v>
+      </c>
+      <c r="H40" t="s">
+        <v>147</v>
+      </c>
+      <c r="J40" t="s">
+        <v>188</v>
+      </c>
+      <c r="K40" t="s">
+        <v>191</v>
+      </c>
+      <c r="N40">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" t="s">
+        <v>148</v>
+      </c>
+      <c r="J41" t="s">
+        <v>189</v>
+      </c>
+      <c r="K41" t="s">
+        <v>191</v>
+      </c>
+      <c r="N41">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" t="s">
+        <v>104</v>
+      </c>
+      <c r="H42" t="s">
+        <v>149</v>
+      </c>
+      <c r="J42" t="s">
+        <v>190</v>
+      </c>
+      <c r="K42" t="s">
+        <v>191</v>
+      </c>
+      <c r="N42">
+        <v>590.1900000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="K43" t="s">
+        <v>192</v>
+      </c>
+      <c r="N43">
+        <v>14164.56</v>
       </c>
     </row>
   </sheetData>

--- a/Unified_PDF_Platform/uploads/extracted_data_structural.xlsx
+++ b/Unified_PDF_Platform/uploads/extracted_data_structural.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="62">
   <si>
     <t>SOURCE_FILE</t>
   </si>
@@ -61,109 +61,130 @@
     <t>ADJUSTMENT_PREMIUM</t>
   </si>
   <si>
-    <t>UHC- Securance- Feb 26 (1).pdf</t>
-  </si>
-  <si>
-    <t>01/07/2026</t>
-  </si>
-  <si>
-    <t>881077749248</t>
-  </si>
-  <si>
-    <t>02/01/2026 - 02/28/2026</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>ASHE</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>DESANDRO</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t>Mathews</t>
-  </si>
-  <si>
-    <t>TEDESCHI</t>
-  </si>
-  <si>
-    <t>Vosper</t>
-  </si>
-  <si>
-    <t>PEGGY</t>
-  </si>
-  <si>
-    <t>PAUL</t>
-  </si>
-  <si>
-    <t>Hannah</t>
-  </si>
-  <si>
-    <t>LORI</t>
-  </si>
-  <si>
-    <t>Shawn K</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>GILLIAN</t>
-  </si>
-  <si>
-    <t>Andrea</t>
-  </si>
-  <si>
-    <t>1088991</t>
-  </si>
-  <si>
-    <t>828700</t>
-  </si>
-  <si>
-    <t>944800</t>
-  </si>
-  <si>
-    <t>359600</t>
-  </si>
-  <si>
-    <t>339500</t>
-  </si>
-  <si>
-    <t>194600</t>
-  </si>
-  <si>
-    <t>980600</t>
-  </si>
-  <si>
-    <t>519600</t>
-  </si>
-  <si>
-    <t>344700</t>
-  </si>
-  <si>
-    <t>HP1650257525B - Admin/Excess Loss</t>
-  </si>
-  <si>
-    <t>HP1650257525B - Max Claims Liability</t>
-  </si>
-  <si>
-    <t>P0157521 - Max Claims Liability</t>
-  </si>
-  <si>
-    <t>P0157521 - Admin/Excess Loss</t>
-  </si>
-  <si>
-    <t>P6000i10021B - Admin/Excess Loss</t>
-  </si>
-  <si>
-    <t>P6000i10021B - Max Claims Liability</t>
+    <t>Unum (Garage Dearborn) Feb 26 2.pdf</t>
+  </si>
+  <si>
+    <t>2022/12/31</t>
+  </si>
+  <si>
+    <t>5362890-0010</t>
+  </si>
+  <si>
+    <t>2022/02/01 - 2022/02/28</t>
+  </si>
+  <si>
+    <t>NAPKA</t>
+  </si>
+  <si>
+    <t>BOOTHE</t>
+  </si>
+  <si>
+    <t>CHARNESKY</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>HOLLOWAY</t>
+  </si>
+  <si>
+    <t>LOCKARD</t>
+  </si>
+  <si>
+    <t>MELDYN</t>
+  </si>
+  <si>
+    <t>MONREAL</t>
+  </si>
+  <si>
+    <t>TASSUM-WENDLING</t>
+  </si>
+  <si>
+    <t>SCHERER</t>
+  </si>
+  <si>
+    <t>SOSNOWSKI</t>
+  </si>
+  <si>
+    <t>KAZCLAW</t>
+  </si>
+  <si>
+    <t>LEANNE</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>MATTHEW</t>
+  </si>
+  <si>
+    <t>DUANE</t>
+  </si>
+  <si>
+    <t>LAWRENCE</t>
+  </si>
+  <si>
+    <t>LAURIE</t>
+  </si>
+  <si>
+    <t>JEFFREY</t>
+  </si>
+  <si>
+    <t>QUENTIN</t>
+  </si>
+  <si>
+    <t>DANIELLE</t>
+  </si>
+  <si>
+    <t>CHERYL</t>
+  </si>
+  <si>
+    <t>JASON</t>
+  </si>
+  <si>
+    <t>KELLY</t>
+  </si>
+  <si>
+    <t>278069173</t>
+  </si>
+  <si>
+    <t>773860583</t>
+  </si>
+  <si>
+    <t>581509973</t>
+  </si>
+  <si>
+    <t>233146770</t>
+  </si>
+  <si>
+    <t>466908173</t>
+  </si>
+  <si>
+    <t>434147943</t>
+  </si>
+  <si>
+    <t>427940863</t>
+  </si>
+  <si>
+    <t>181287773</t>
+  </si>
+  <si>
+    <t>263812283</t>
+  </si>
+  <si>
+    <t>975269563</t>
+  </si>
+  <si>
+    <t>711908673</t>
+  </si>
+  <si>
+    <t>331949563</t>
+  </si>
+  <si>
+    <t>DTS</t>
+  </si>
+  <si>
+    <t>DTL</t>
   </si>
   <si>
     <t>TOTAL CURRENT PREMIUM</t>
@@ -172,10 +193,13 @@
     <t>GRAND TOTAL (COMBINED)</t>
   </si>
   <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>LTD</t>
+  </si>
+  <si>
     <t>EE</t>
-  </si>
-  <si>
-    <t>EC</t>
   </si>
 </sst>
 </file>
@@ -533,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -600,22 +624,22 @@
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="L2" t="s">
+        <v>59</v>
       </c>
       <c r="M2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N2">
-        <v>577.4400000000001</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -632,25 +656,25 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N3">
-        <v>378.14</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -667,25 +691,25 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>59</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N4">
-        <v>584.4299999999999</v>
+        <v>30.64</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -702,25 +726,25 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="L5" t="s">
+        <v>60</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N5">
-        <v>750.8099999999999</v>
+        <v>134.83</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -737,25 +761,25 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>55</v>
+      </c>
+      <c r="L6" t="s">
+        <v>59</v>
       </c>
       <c r="M6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N6">
-        <v>584.4299999999999</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -772,25 +796,25 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
         <v>35</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>60</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N7">
-        <v>750.8099999999999</v>
+        <v>85.27</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -807,25 +831,25 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" t="s">
         <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>55</v>
+      </c>
+      <c r="L8" t="s">
+        <v>59</v>
       </c>
       <c r="M8" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N8">
-        <v>497.25</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -842,25 +866,25 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s">
-        <v>49</v>
+        <v>56</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N9">
-        <v>318.85</v>
+        <v>114.13</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -877,25 +901,25 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="L10" t="s">
+        <v>59</v>
       </c>
       <c r="M10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N10">
-        <v>577.4400000000001</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -912,25 +936,25 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N11">
-        <v>378.14</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -947,25 +971,25 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="L12" t="s">
+        <v>60</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N12">
-        <v>584.4299999999999</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -982,25 +1006,25 @@
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
+        <v>55</v>
+      </c>
+      <c r="L13" t="s">
+        <v>59</v>
       </c>
       <c r="M13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N13">
-        <v>750.8099999999999</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1017,25 +1041,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K14" t="s">
-        <v>48</v>
+        <v>56</v>
+      </c>
+      <c r="L14" t="s">
+        <v>60</v>
       </c>
       <c r="M14" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N14">
-        <v>497.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1052,25 +1076,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
       </c>
       <c r="M15" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N15">
-        <v>318.85</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1087,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J16" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>55</v>
+      </c>
+      <c r="L16" t="s">
+        <v>59</v>
       </c>
       <c r="M16" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N16">
-        <v>913.35</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1122,41 +1146,111 @@
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J17" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K17" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="L17" t="s">
+        <v>59</v>
       </c>
       <c r="M17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N17">
-        <v>609.01</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>54</v>
+      </c>
       <c r="K18" t="s">
-        <v>50</v>
+        <v>56</v>
+      </c>
+      <c r="L18" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18" t="s">
+        <v>61</v>
       </c>
       <c r="N18">
-        <v>9071.440000000002</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" t="s">
+        <v>54</v>
+      </c>
       <c r="K19" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="L19" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" t="s">
+        <v>61</v>
       </c>
       <c r="N19">
-        <v>9071.440000000002</v>
+        <v>34.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="K20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20">
+        <v>903.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="K21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21">
+        <v>903.8</v>
       </c>
     </row>
   </sheetData>
